--- a/海龟汤_问卷_SoupData.xlsx
+++ b/海龟汤_问卷_SoupData.xlsx
@@ -383,21 +383,17 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>我要测试。</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B2"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>这是新的测试。</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -412,69 +408,108 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>访客 57789</t>
+          <t>访客 99440</t>
         </is>
       </c>
       <c r="H2" s="2">
-        <v>46185.870405092595</v>
+        <v>46185.87056712963</v>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3"/>
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>怀孕</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>爱人怀孕好几个月啦，我听着孩子的胎动，兴奋不已，虽然爱人日渐消瘦，但ta应该能理解我了...</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>我怀了宝宝，但他却背叛了我，害得我在悲痛中失去了孩子，我恨他，我要让他知道我的不易，我偷偷喂他喝下了好多蛔虫卵，把他绑在床上每天提供着“孩子”所需的养分，看着他因蛔虫繁殖而逐渐隆起的肚子，这下他应该能理解我了吧...</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>访客 99440</t>
+          <t>访客 55856</t>
         </is>
       </c>
       <c r="H3" s="2">
-        <v>46185.87056712963</v>
+        <v>46185.884097222224</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
       <c r="A4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>怀孕</t>
+          <t>规则和指南-必看!!!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>爱人怀孕好几个月啦，我听着孩子的胎动，兴奋不已，虽然爱人日渐消瘦，但ta应该能理解我了...</t>
+          <t>游戏规则很简单：
+由[c]主持人[/]给出一个简单的故事背景（简称[r]汤面[/]）。
+而[y]其他人则需要不停地提问[/]，从而还原出完整的故事。
+其中[c]主持人[/]只能回答：
+(是)、(不是)、(是也不是) 或者 (不重要)。
+[r]最后完全还原出故事真相就算成功！[/]
+本世界内，你也可以在个人平板的"传汤"页面手动输入汤面/汤底到队列中哦！
+你也可以通过以下链接上传海龟汤到云端，经过审核后就可以在"选汤"页面永久看到你的汤啦！
+https://my.feishu.cn/share/base/form/shrcn7pZg4bhxYsBF6x0Q7lm0ab</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>我怀了宝宝，但他却背叛了我，害得我在悲痛中失去了孩子，我恨他，我要让他知道我的不易，我偷偷喂他喝下了好多蛔虫卵，把他绑在床上每天提供着“孩子”所需的养分，看着他因蛔虫繁殖而逐渐隆起的肚子，这下他应该能理解我了吧...</t>
+          <t>[t]文本排版与颜色[/]
+注意：实际打字时，请务必将以下示例中的中文全角［］切换为英文半角[]才会生效。
+1. 结构标签规则
+放大的标题和副标题需要标签包裹，正文直接书写即可：
+• [r]［t］大标题内容［/］[/]
+• [r]［st］副标题内容［/］[/]
+2. 换行分段规则
+在输入框内打字时，直接按下[r]【回车键】[/]即可换行。
+3. 文字变色规则
+用颜色标签包裹需要变色的文字
+• [r]［颜色首字母］你要写的字［/］[/]
+支持的颜色首字母有：
+[r]r[/]（红）、[o]o[/]（橙）、[y]y[/]（黄）、[g]g[/]（绿）、[c]c[/]（青）、[b]b[/]（蓝）、[p]p[/]（紫）
+----------------------------------
+[t]
+举例:
+[/]
+输入内容为：
+----------------------------------
+［st］提示信息［/］
+游戏即将开始，
+请大家［y］做好准备［/］。
+----------------------------------
+显示内容为：
+----------------------------------
+[st]提示信息[/]
+游戏即将开始，
+请大家[y]做好准备[/]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -484,11 +519,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>访客 55856</t>
+          <t>访客 77896</t>
         </is>
       </c>
       <c r="H4" s="2">
-        <v>46185.884097222224</v>
+        <v>46185.89811342592</v>
       </c>
     </row>
   </sheetData>

--- a/海龟汤_问卷_SoupData.xlsx
+++ b/海龟汤_问卷_SoupData.xlsx
@@ -383,86 +383,14 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2"/>
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>规则和指南-必看!!!</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>访客 99440</t>
-        </is>
-      </c>
-      <c r="H2" s="2">
-        <v>46185.87056712963</v>
-      </c>
-    </row>
-    <row r="3" ht="25.5" customHeight="1">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>怀孕</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>爱人怀孕好几个月啦，我听着孩子的胎动，兴奋不已，虽然爱人日渐消瘦，但ta应该能理解我了...</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>我怀了宝宝，但他却背叛了我，害得我在悲痛中失去了孩子，我恨他，我要让他知道我的不易，我偷偷喂他喝下了好多蛔虫卵，把他绑在床上每天提供着“孩子”所需的养分，看着他因蛔虫繁殖而逐渐隆起的肚子，这下他应该能理解我了吧...</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>访客 55856</t>
-        </is>
-      </c>
-      <c r="H3" s="2">
-        <v>46185.884097222224</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>规则和指南-必看!!!</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t>游戏规则很简单：
 由[c]主持人[/]给出一个简单的故事背景（简称[r]汤面[/]）。
@@ -475,7 +403,7 @@
 https://my.feishu.cn/share/base/form/shrcn7pZg4bhxYsBF6x0Q7lm0ab</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>[t]文本排版与颜色[/]
 注意：实际打字时，请务必将以下示例中的中文全角［］切换为英文半角[]才会生效。
@@ -507,28 +435,66 @@
 请大家[y]做好准备[/]</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>简单</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>访客 77896</t>
         </is>
       </c>
-      <c r="H4" s="2">
+      <c r="H2" s="2">
         <v>46185.89811342592</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5" customHeight="1">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>怀孕</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>爱人怀孕好几个月啦，我听着孩子的胎动，兴奋不已，虽然爱人日渐消瘦，但ta应该能理解我了...</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>我怀了宝宝，但他却背叛了我，害得我在悲痛中失去了孩子，我恨他，我要让他知道我的不易，我偷偷喂他喝下了好多蛔虫卵，把他绑在床上每天提供着“孩子”所需的养分，看着他因蛔虫繁殖而逐渐隆起的肚子，这下他应该能理解我了吧...</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>访客 55856</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <v>46185.884097222224</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" sqref="E2:E3" type="list">
+    <dataValidation allowBlank="false" sqref="E2:E2" type="list">
       <formula1>"简单,中等,困难"</formula1>
     </dataValidation>
   </dataValidations>
